--- a/data/trans_camb/P16A04-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A04-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 3,08</t>
+          <t>-1,59; 3,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 3,66</t>
+          <t>-1,2; 3,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,88</t>
+          <t>-2,37; 0,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 3,9</t>
+          <t>-0,54; 3,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,41</t>
+          <t>-1,28; 2,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,2</t>
+          <t>1,24; 5,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,62</t>
+          <t>-0,79; 2,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,23</t>
+          <t>-0,86; 2,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 2,29</t>
+          <t>-0,34; 2,39</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,21; 258,13</t>
+          <t>-54,63; 285,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 310,59</t>
+          <t>-43,67; 307,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-75,68; 94,43</t>
+          <t>-72,85; 108,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 1247,13</t>
+          <t>-54,33; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,54; 1387,4</t>
+          <t>39,76; 1422,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,26; 244,94</t>
+          <t>-36,45; 233,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 210,22</t>
+          <t>-42,19; 198,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,22; 223,78</t>
+          <t>-19,15; 230,75</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 2,71</t>
+          <t>-0,8; 2,56</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,66</t>
+          <t>-0,69; 2,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,0</t>
+          <t>-0,75; 2,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 1,75</t>
+          <t>-2,67; 1,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 0,67</t>
+          <t>-3,56; 0,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,83</t>
+          <t>-3,1; 0,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,44</t>
+          <t>-1,32; 1,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,18</t>
+          <t>-1,56; 1,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,1</t>
+          <t>-1,4; 1,0</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,41; 741,47</t>
+          <t>-62,0; 798,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,73; 738,53</t>
+          <t>-62,09; 780,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,84; 656,73</t>
+          <t>-52,35; 727,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-73,45; 154,27</t>
+          <t>-68,88; 125,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,46; 73,37</t>
+          <t>-89,18; 82,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,81; 57,65</t>
+          <t>-78,0; 64,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,34; 133,71</t>
+          <t>-50,04; 112,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,65; 103,52</t>
+          <t>-64,23; 85,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-51,12; 110,86</t>
+          <t>-56,05; 90,3</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 4,34</t>
+          <t>0,21; 4,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,96</t>
+          <t>-1,85; 0,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 3,82</t>
+          <t>-1,39; 4,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 2,4</t>
+          <t>-4,46; 2,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 6,09</t>
+          <t>-3,42; 6,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 5,29</t>
+          <t>-2,73; 4,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,25</t>
+          <t>-0,18; 3,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,6</t>
+          <t>-1,59; 1,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,65</t>
+          <t>-1,53; 3,56</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 417,67</t>
+          <t>0,81; 510,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,19; 115,48</t>
+          <t>-79,25; 107,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,39; 318,14</t>
+          <t>-52,61; 341,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-80,4; 172,04</t>
+          <t>-77,36; 212,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,05; 414,85</t>
+          <t>-74,94; 434,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,46; 329,21</t>
+          <t>-49,46; 289,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 232,51</t>
+          <t>-13,13; 241,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-56,92; 107,32</t>
+          <t>-58,34; 120,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-45,84; 220,06</t>
+          <t>-44,86; 216,28</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,69</t>
+          <t>-0,14; 2,54</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,69</t>
+          <t>-0,77; 1,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,27</t>
+          <t>-0,9; 1,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,57</t>
+          <t>-0,16; 3,94</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 2,3</t>
+          <t>-1,2; 2,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,81</t>
+          <t>-2,73; 0,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,5</t>
+          <t>0,3; 2,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 1,5</t>
+          <t>-0,53; 1,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,87</t>
+          <t>-1,22; 0,75</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 189,51</t>
+          <t>-6,77; 182,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,07; 131,96</t>
+          <t>-31,42; 127,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 89,43</t>
+          <t>-40,09; 98,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 179,37</t>
+          <t>-7,6; 199,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,56; 116,37</t>
+          <t>-34,53; 111,74</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,97; 37,32</t>
+          <t>-68,05; 37,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,71; 142,04</t>
+          <t>8,89; 149,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 86,64</t>
+          <t>-20,25; 79,18</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,09; 49,22</t>
+          <t>-44,01; 42,19</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 2,62</t>
+          <t>-2,45; 2,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 0,83</t>
+          <t>-3,33; 1,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,9</t>
+          <t>-3,46; 0,92</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,37</t>
+          <t>-2,11; 1,59</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 1,79</t>
+          <t>-1,86; 1,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 4,21</t>
+          <t>-0,3; 4,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 1,42</t>
+          <t>-1,41; 1,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,87</t>
+          <t>-1,75; 0,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 2,28</t>
+          <t>-0,84; 2,26</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-51,64; 157,38</t>
+          <t>-54,44; 138,6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-75,08; 53,39</t>
+          <t>-74,37; 57,66</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-73,36; 71,42</t>
+          <t>-74,12; 67,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-61,94; 98,73</t>
+          <t>-59,73; 121,47</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-53,33; 126,06</t>
+          <t>-54,28; 119,62</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 281,95</t>
+          <t>-15,69; 305,7</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-42,44; 80,12</t>
+          <t>-41,34; 79,03</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-50,42; 56,73</t>
+          <t>-51,31; 54,53</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,39; 120,73</t>
+          <t>-25,25; 125,8</t>
         </is>
       </c>
     </row>
@@ -1757,37 +1757,37 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,12</t>
+          <t>-1,05; 2,04</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,03</t>
+          <t>-0,98; 2,1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,06; 8,21</t>
+          <t>0,52; 9,54</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 2,02</t>
+          <t>-0,33; 2,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,89</t>
+          <t>-1,16; 1,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,72</t>
+          <t>-0,57; 1,85</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,61</t>
+          <t>-0,42; 1,72</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,67</t>
+          <t>0,02; 2,53</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-17,24; 144,85</t>
+          <t>-16,29; 154,67</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-54,27; 74,59</t>
+          <t>-52,79; 79,63</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-23,41; 135,68</t>
+          <t>-25,81; 145,25</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 140,79</t>
+          <t>-21,07; 152,91</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-47,78; 81,02</t>
+          <t>-48,18; 87,18</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1,11; 212,14</t>
+          <t>-3,71; 205,82</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,85</t>
+          <t>0,31; 1,87</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,9</t>
+          <t>-0,5; 0,88</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,12</t>
+          <t>-0,35; 1,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,39</t>
+          <t>-0,18; 1,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,77</t>
+          <t>-0,72; 0,75</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,58</t>
+          <t>-0,09; 1,61</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,43</t>
+          <t>0,35; 1,41</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,63</t>
+          <t>-0,35; 0,64</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,17</t>
+          <t>-0,05; 1,11</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>10,13; 121,11</t>
+          <t>14,55; 123,67</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 60,79</t>
+          <t>-22,96; 59,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 73,42</t>
+          <t>-16,52; 81,93</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 75,71</t>
+          <t>-7,42; 74,01</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 40,58</t>
+          <t>-27,11; 39,69</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 85,69</t>
+          <t>-3,02; 88,46</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,58; 78,81</t>
+          <t>14,8; 81,18</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 35,07</t>
+          <t>-16,16; 36,48</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1,49; 64,61</t>
+          <t>-2,85; 60,42</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A04-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P16A04-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>1,0</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,25</t>
+          <t>-1,68; 3,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,25</t>
+          <t>-1,01; 3,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,92</t>
+          <t>-2,68; 0,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,85</t>
+          <t>-0,47; 3,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,32</t>
+          <t>-1,3; 2,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,09</t>
+          <t>1,13; 5,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,54</t>
+          <t>-0,69; 2,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,16</t>
+          <t>-0,85; 2,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,39</t>
+          <t>-0,37; 2,18</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-31,3%</t>
+          <t>-30,86%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>310,52%</t>
+          <t>304,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-54,63; 285,99</t>
+          <t>-59,61; 238,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,67; 307,24</t>
+          <t>-45,5; 270,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-72,85; 108,94</t>
+          <t>-76,95; 75,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,33; —</t>
+          <t>-53,24; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>39,76; 1422,27</t>
+          <t>31,31; 1471,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 233,32</t>
+          <t>-33,04; 251,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,19; 198,01</t>
+          <t>-39,35; 228,73</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 230,75</t>
+          <t>-18,94; 218,34</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-0,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,56</t>
+          <t>-0,7; 2,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,69</t>
+          <t>-0,75; 2,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,3</t>
+          <t>-0,9; 1,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 1,69</t>
+          <t>-2,81; 1,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,55</t>
+          <t>-3,28; 0,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 0,87</t>
+          <t>-3,06; 0,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,45</t>
+          <t>-1,15; 1,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,05</t>
+          <t>-1,55; 1,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,0</t>
+          <t>-1,52; 0,91</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-33,59%</t>
+          <t>-37,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-7,61%</t>
+          <t>-11,67%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,0; 798,12</t>
+          <t>-56,57; 702,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 780,14</t>
+          <t>-66,66; 770,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-52,35; 727,47</t>
+          <t>-59,49; 529,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,88; 125,03</t>
+          <t>-74,98; 133,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-89,18; 82,74</t>
+          <t>-88,51; 52,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,0; 64,98</t>
+          <t>-79,38; 72,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-50,04; 112,42</t>
+          <t>-50,86; 126,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-64,23; 85,29</t>
+          <t>-64,38; 98,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,05; 90,3</t>
+          <t>-58,0; 81,59</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,39</t>
+          <t>2,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 4,24</t>
+          <t>0,24; 4,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 0,92</t>
+          <t>-1,79; 0,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,24</t>
+          <t>0,95; 5,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 2,56</t>
+          <t>-4,58; 2,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 6,27</t>
+          <t>-3,26; 6,19</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 4,72</t>
+          <t>-2,59; 5,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 3,28</t>
+          <t>-0,15; 3,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,53</t>
+          <t>-1,66; 1,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 3,56</t>
+          <t>0,61; 4,45</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>173,29%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>121,99%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 510,24</t>
+          <t>1,65; 442,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,25; 107,24</t>
+          <t>-80,34; 96,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,61; 341,85</t>
+          <t>25,7; 505,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-77,36; 212,2</t>
+          <t>-77,32; 158,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-74,94; 434,27</t>
+          <t>-68,79; 350,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-49,46; 289,62</t>
+          <t>-48,67; 343,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 241,66</t>
+          <t>-13,31; 213,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,34; 120,67</t>
+          <t>-62,27; 103,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-44,86; 216,28</t>
+          <t>13,39; 319,8</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>0,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,54</t>
+          <t>-0,16; 2,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,63</t>
+          <t>-0,81; 1,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,31</t>
+          <t>-0,83; 1,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,94</t>
+          <t>-0,29; 3,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,3</t>
+          <t>-1,32; 2,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 0,74</t>
+          <t>-1,81; 1,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,59</t>
+          <t>0,31; 2,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,45</t>
+          <t>-0,42; 1,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,75</t>
+          <t>-0,59; 1,43</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-24,38%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-7,29%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 182,41</t>
+          <t>-10,27; 170,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 127,67</t>
+          <t>-33,58; 111,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,09; 98,9</t>
+          <t>-36,06; 123,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 199,25</t>
+          <t>-10,98; 204,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,53; 111,74</t>
+          <t>-37,86; 114,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,05; 37,97</t>
+          <t>-42,09; 73,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,89; 149,36</t>
+          <t>10,75; 143,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 79,18</t>
+          <t>-16,06; 90,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-44,01; 42,19</t>
+          <t>-22,57; 80,04</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,11</t>
+          <t>-1,29</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>0,55</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,34</t>
+          <t>-1,94; 2,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 1,06</t>
+          <t>-3,37; 1,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 0,92</t>
+          <t>-3,6; 0,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,59</t>
+          <t>-2,22; 1,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 1,74</t>
+          <t>-1,82; 1,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,46</t>
+          <t>-0,14; 3,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 1,4</t>
+          <t>-1,56; 1,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,97</t>
+          <t>-1,79; 0,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 2,26</t>
+          <t>-0,77; 1,96</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-36,7%</t>
+          <t>-42,83%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-54,44; 138,6</t>
+          <t>-44,31; 144,42</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-74,37; 57,66</t>
+          <t>-73,28; 64,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-74,12; 67,96</t>
+          <t>-75,9; 47,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-59,73; 121,47</t>
+          <t>-65,16; 103,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-54,28; 119,62</t>
+          <t>-53,89; 127,54</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-15,69; 305,7</t>
+          <t>-6,57; 272,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-41,34; 79,03</t>
+          <t>-44,78; 69,06</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-51,31; 54,53</t>
+          <t>-52,22; 48,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,25; 125,8</t>
+          <t>-23,31; 107,3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,94</t>
+          <t>2,76</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,25</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 2,04</t>
+          <t>-0,94; 2,12</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,1</t>
+          <t>-0,91; 2,04</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,52; 9,54</t>
+          <t>-0,0; 8,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 2,02</t>
+          <t>-0,37; 1,95</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,07</t>
+          <t>-1,18; 0,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,85</t>
+          <t>-0,31; 2,22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,72</t>
+          <t>-0,28; 1,75</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,97</t>
+          <t>-0,97; 0,92</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,02; 2,53</t>
+          <t>0,14; 2,84</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>455,85%</t>
+          <t>428,73%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 154,67</t>
+          <t>-18,98; 134,19</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-52,79; 79,63</t>
+          <t>-51,01; 76,59</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-25,81; 145,25</t>
+          <t>-19,23; 162,03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 152,91</t>
+          <t>-16,84; 159,85</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-48,18; 87,18</t>
+          <t>-48,84; 79,64</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 205,82</t>
+          <t>4,44; 240,02</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,81</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,87</t>
+          <t>0,35; 1,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,88</t>
+          <t>-0,46; 0,88</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,19</t>
+          <t>-0,23; 1,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,44</t>
+          <t>-0,12; 1,38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,75</t>
+          <t>-0,68; 0,74</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 1,61</t>
+          <t>0,38; 1,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,41</t>
+          <t>0,26; 1,39</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,64</t>
+          <t>-0,34; 0,68</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,11</t>
+          <t>0,3; 1,32</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>40,32%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>14,55; 123,67</t>
+          <t>16,29; 126,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-22,96; 59,44</t>
+          <t>-22,41; 59,34</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-16,52; 81,93</t>
+          <t>-11,82; 82,0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 74,01</t>
+          <t>-5,24; 73,93</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 39,69</t>
+          <t>-26,04; 39,8</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 88,46</t>
+          <t>14,87; 93,88</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,8; 81,18</t>
+          <t>10,66; 77,17</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 36,48</t>
+          <t>-14,58; 39,8</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 60,42</t>
+          <t>13,26; 74,8</t>
         </is>
       </c>
     </row>
